--- a/data/trans_orig/P43D-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P43D-Estudios-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,25 +526,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última citología vaginal que le hicieron en 2007</t>
+          <t>Población según el tiempo transcurrido desde la última citología vaginal que le hicieron en 2007 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +548,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -564,17 +557,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -645,41 +627,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -702,13 +649,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -723,37 +663,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>212</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>212781</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>189154</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>234509</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>191862</t>
+          <t>189154</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>237211</t>
+          <t>234509</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,47 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>212781</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>191862</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>237211</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>41,13%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>37,09%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>45,85%</t>
+          <t>45,33%</t>
         </is>
       </c>
     </row>
@@ -836,37 +741,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>143</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>141675</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>123557</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>163659</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>121781</t>
+          <t>123557</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>160977</t>
+          <t>163659</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,47 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>141675</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>121781</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>160977</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>27,38%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>23,54%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>31,12%</t>
+          <t>31,63%</t>
         </is>
       </c>
     </row>
@@ -949,37 +819,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>109</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>109232</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>91220</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129154</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +864,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>92985</t>
+          <t>91220</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>128211</t>
+          <t>129154</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,47 +879,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>109232</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>92985</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>128211</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>21,11%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>17,97%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>24,78%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -1062,37 +897,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53668</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42039</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67707</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +942,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40022</t>
+          <t>42039</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68733</t>
+          <t>67707</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,47 +957,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>53668</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>40022</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>68733</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>10,37%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>13,29%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -1175,37 +975,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>518</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>517357</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>517357</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>517357</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1239,41 +1039,6 @@
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>518</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>517357</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>517357</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>517357</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1292,37 +1057,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>168930</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>144204</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>193365</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>146293</t>
+          <t>144204</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>194222</t>
+          <t>193365</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,47 +1117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>168930</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>146293</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>194222</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>18,02%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>15,61%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>20,72%</t>
+          <t>20,63%</t>
         </is>
       </c>
     </row>
@@ -1405,37 +1135,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>305</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>312377</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>284222</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>343851</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1180,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>287234</t>
+          <t>284222</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>339812</t>
+          <t>343851</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,47 +1195,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>312377</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>287234</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>339812</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>33,32%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>30,64%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -1518,37 +1213,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>257</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>263636</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>234307</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>291327</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1258,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>235345</t>
+          <t>234307</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>290168</t>
+          <t>291327</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,47 +1273,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>263636</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>235345</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>290168</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>28,12%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>25,11%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>30,96%</t>
+          <t>31,08%</t>
         </is>
       </c>
     </row>
@@ -1631,37 +1291,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>184</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>192440</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>168434</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>218707</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1336,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>168339</t>
+          <t>168434</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>217149</t>
+          <t>218707</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,47 +1351,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>192440</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>168339</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>217149</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>20,53%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>17,96%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>23,17%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -1744,37 +1369,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>905</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>937383</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>937383</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>937383</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1808,41 +1433,6 @@
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>905</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>937383</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>937383</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>937383</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1861,37 +1451,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39828</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29023</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1496,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29862</t>
+          <t>29023</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53744</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,47 +1511,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>39828</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>29862</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>53744</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>12,28%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>16,57%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -1974,37 +1529,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>100002</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84602</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>117539</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +1574,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>83688</t>
+          <t>84602</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>118217</t>
+          <t>117539</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,47 +1589,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>100002</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>83688</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>118217</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>30,83%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>25,8%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>36,45%</t>
+          <t>36,24%</t>
         </is>
       </c>
     </row>
@@ -2087,37 +1607,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>98812</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>81915</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>114786</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +1652,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80609</t>
+          <t>81915</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114722</t>
+          <t>114786</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,47 +1667,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>98812</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>80609</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>114722</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>30,46%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>24,85%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>35,37%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -2200,37 +1685,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>85727</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>70616</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101345</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +1730,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68916</t>
+          <t>70616</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>100808</t>
+          <t>101345</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,47 +1745,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>85727</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>68916</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>100808</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>26,43%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>21,25%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>31,08%</t>
+          <t>31,24%</t>
         </is>
       </c>
     </row>
@@ -2313,37 +1763,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>307</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>324369</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>324369</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>324369</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2377,41 +1827,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>324369</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>324369</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>324369</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2430,37 +1845,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>410</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>421540</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>388118</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>459721</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +1890,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>385200</t>
+          <t>388118</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>456868</t>
+          <t>459721</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,47 +1905,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>421540</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>385200</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>456868</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>23,69%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>21,65%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>25,68%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -2543,37 +1923,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>542</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>554054</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>515341</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>596654</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +1968,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>514394</t>
+          <t>515341</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>593918</t>
+          <t>596654</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,47 +1983,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>542</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>554054</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>514394</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>593918</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>31,14%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>28,91%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>33,38%</t>
+          <t>33,54%</t>
         </is>
       </c>
     </row>
@@ -2656,37 +2001,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>460</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>471680</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>430680</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>505487</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2046,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>433880</t>
+          <t>430680</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>509727</t>
+          <t>505487</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,47 +2061,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>460</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>471680</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>433880</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>509727</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>26,51%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>24,39%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>28,65%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -2769,37 +2079,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>318</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>331836</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>298182</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>364568</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2124,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>295845</t>
+          <t>298182</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>365073</t>
+          <t>364568</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,47 +2139,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>331836</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>295845</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>365073</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>18,65%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>16,63%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>20,52%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -2882,37 +2157,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1779109</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1779109</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1779109</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2946,41 +2221,6 @@
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1730</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1779109</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1779109</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1779109</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2994,13 +2234,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A9:A13"/>
     <mergeCell ref="A4:A8"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A19:A23"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="C1:I1"/>
   </mergeCells>
@@ -3014,7 +2253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3033,25 +2272,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última citología vaginal que le hicieron en 2012</t>
+          <t>Población según el tiempo transcurrido desde la última citología vaginal que le hicieron en 2012 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3062,7 +2294,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3071,17 +2303,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -3152,41 +2373,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -3209,13 +2395,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3230,37 +2409,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>198</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214229</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>191704</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>240056</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +2454,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>190131</t>
+          <t>191704</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>239458</t>
+          <t>240056</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,47 +2469,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>214229</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>190131</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>239458</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>30,45%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>27,03%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>34,04%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -3343,37 +2487,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>218</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>231254</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>205760</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>257458</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +2532,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>207460</t>
+          <t>205760</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>256952</t>
+          <t>257458</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,47 +2547,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>231254</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>207460</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>256952</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>32,87%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>29,49%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>36,52%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -3456,37 +2565,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>153064</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>131095</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>173822</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +2610,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>130068</t>
+          <t>131095</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>175864</t>
+          <t>173822</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,47 +2625,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>153064</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>130068</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>175864</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>21,76%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>18,49%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>25,0%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -3569,37 +2643,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>104973</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>86023</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>126226</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +2688,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88878</t>
+          <t>86023</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>127173</t>
+          <t>126226</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,47 +2703,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>104973</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>88878</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>127173</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>14,92%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>12,63%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>18,08%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -3682,37 +2721,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>657</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>703520</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>703520</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>703520</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3746,41 +2785,6 @@
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>657</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>703520</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>703520</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>703520</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3799,37 +2803,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>181</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>195840</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>170703</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>223749</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +2848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>172893</t>
+          <t>170703</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>223636</t>
+          <t>223749</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,47 +2863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>195840</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>172893</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>223636</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>15,84%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>13,98%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>18,09%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -3912,37 +2881,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>416</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>451375</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>419048</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>488666</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +2926,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>416397</t>
+          <t>419048</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>488346</t>
+          <t>488666</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,47 +2941,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>451375</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>416397</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>488346</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>36,5%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>33,68%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>39,49%</t>
+          <t>39,52%</t>
         </is>
       </c>
     </row>
@@ -4025,37 +2959,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>328</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>355702</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>324652</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>394753</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +3004,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>324248</t>
+          <t>324652</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>393138</t>
+          <t>394753</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,47 +3019,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>355702</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>324248</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>393138</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>28,77%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>26,22%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>31,79%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -4138,37 +3037,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>210</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>233592</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>205572</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>265282</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +3082,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>206735</t>
+          <t>205572</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>264807</t>
+          <t>265282</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,47 +3097,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>233592</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>206735</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>264807</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>18,89%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>16,72%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>21,42%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -4251,37 +3115,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1236509</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1236509</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1236509</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4315,41 +3179,6 @@
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1135</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1236509</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1236509</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1236509</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4368,37 +3197,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35164</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23379</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>48868</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +3242,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23966</t>
+          <t>23379</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47505</t>
+          <t>48868</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,47 +3257,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>35164</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>23966</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>47505</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>10,14%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>6,91%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -4481,37 +3275,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>107721</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>88966</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>126520</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +3320,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>90390</t>
+          <t>88966</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>127439</t>
+          <t>126520</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,47 +3335,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>107721</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>90390</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>127439</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>31,05%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>26,05%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>36,73%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -4594,37 +3353,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>112</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>128049</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>109674</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>147130</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +3398,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>109809</t>
+          <t>109674</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>147476</t>
+          <t>147130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,47 +3413,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>128049</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>109809</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>147476</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>36,91%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>31,65%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>42,51%</t>
+          <t>42,41%</t>
         </is>
       </c>
     </row>
@@ -4707,37 +3431,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75991</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>61307</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>94205</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +3476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59790</t>
+          <t>61307</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92544</t>
+          <t>94205</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,47 +3491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>75991</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>59790</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>92544</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>21,9%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>26,68%</t>
+          <t>27,15%</t>
         </is>
       </c>
     </row>
@@ -4820,37 +3509,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>309</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>346924</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>346924</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>346924</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4884,41 +3573,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>346924</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>346924</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>346924</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4937,37 +3591,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>410</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>445233</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>404683</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>485935</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +3636,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>409181</t>
+          <t>404683</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>483555</t>
+          <t>485935</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,47 +3651,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>445233</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>409181</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>483555</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>19,47%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>17,89%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>21,14%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -5050,37 +3669,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>731</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>790349</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>743786</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>840407</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +3714,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>747605</t>
+          <t>743786</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>839673</t>
+          <t>840407</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,47 +3729,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>731</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>790349</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>747605</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>839673</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>34,56%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>32,69%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>36,72%</t>
+          <t>36,75%</t>
         </is>
       </c>
     </row>
@@ -5163,37 +3747,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>584</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>636815</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>591682</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>684427</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +3792,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>596530</t>
+          <t>591682</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>687451</t>
+          <t>684427</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,47 +3807,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>584</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>636815</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>596530</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>687451</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>27,85%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>26,08%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>30,06%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -5276,37 +3825,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>376</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>414556</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>374451</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>454898</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +3870,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>380488</t>
+          <t>374451</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>454438</t>
+          <t>454898</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,47 +3885,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>414556</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>380488</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>454438</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>18,13%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>16,64%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>19,87%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -5389,37 +3903,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2101</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2286953</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2286953</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2286953</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5453,41 +3967,6 @@
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2101</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>2286953</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>2286953</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>2286953</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5501,13 +3980,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A9:A13"/>
     <mergeCell ref="A4:A8"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A19:A23"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="C1:I1"/>
   </mergeCells>
@@ -5521,7 +3999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5540,25 +4018,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última citología vaginal que le hicieron en 2016</t>
+          <t>Población según el tiempo transcurrido desde la última citología vaginal que le hicieron en 2016 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5569,7 +4040,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5578,17 +4049,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -5659,41 +4119,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -5716,13 +4141,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -5737,37 +4155,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>199</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>228359</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>203260</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>249716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +4200,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>204895</t>
+          <t>203260</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>252259</t>
+          <t>249716</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,47 +4215,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>228359</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>204895</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>252259</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>45,44%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>40,77%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>50,19%</t>
+          <t>49,69%</t>
         </is>
       </c>
     </row>
@@ -5850,37 +4233,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>157</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>165352</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>143531</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>186376</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +4278,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>146249</t>
+          <t>143531</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>189951</t>
+          <t>186376</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,47 +4293,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>165352</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>146249</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>189951</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>32,9%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>29,1%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>37,8%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -5963,37 +4311,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>73567</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59404</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>92143</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +4356,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58832</t>
+          <t>59404</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>90611</t>
+          <t>92143</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,47 +4371,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>73567</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>58832</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>90611</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>14,64%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>11,71%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>18,03%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -6076,37 +4389,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35301</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24948</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47046</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23921</t>
+          <t>24948</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47604</t>
+          <t>47046</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,47 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>35301</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>23921</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>47604</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>9,47%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -6189,37 +4467,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>460</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>502579</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>502579</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>502579</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6253,41 +4531,6 @@
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>460</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>502579</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>502579</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>502579</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6306,37 +4549,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>249</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>262853</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>235367</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>293629</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +4594,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>236446</t>
+          <t>235367</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>290917</t>
+          <t>293629</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,47 +4609,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>262853</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>236446</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>290917</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>20,17%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>18,15%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>22,33%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -6419,37 +4627,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>558</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>581536</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>545347</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>618860</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +4672,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>544390</t>
+          <t>545347</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>619393</t>
+          <t>618860</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,47 +4687,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>558</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>581536</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>544390</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>619393</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>44,63%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>41,78%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>47,53%</t>
+          <t>47,49%</t>
         </is>
       </c>
     </row>
@@ -6532,37 +4705,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>277</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>284949</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>256324</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>316384</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +4750,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>257691</t>
+          <t>256324</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>313150</t>
+          <t>316384</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,47 +4765,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>284949</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>257691</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>313150</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>21,87%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>19,78%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>24,03%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -6645,37 +4783,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>166</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>173704</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>149235</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>201448</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +4828,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>149825</t>
+          <t>149235</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>199323</t>
+          <t>201448</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,47 +4843,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>173704</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>149825</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>199323</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>13,33%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>11,5%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>15,3%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -6758,37 +4861,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1303042</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1303042</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1303042</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6822,41 +4925,6 @@
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1250</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1303042</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1303042</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1303042</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6875,37 +4943,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39715</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28605</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53999</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +4988,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27874</t>
+          <t>28605</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52981</t>
+          <t>53999</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,47 +5003,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>39715</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>27874</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>52981</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>9,36%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>12,49%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -6988,37 +5021,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>167</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>177967</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>157627</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>198055</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +5066,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>158253</t>
+          <t>157627</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>200697</t>
+          <t>198055</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,47 +5081,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>177967</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>158253</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>200697</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>41,96%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>37,32%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>47,32%</t>
+          <t>46,7%</t>
         </is>
       </c>
     </row>
@@ -7101,37 +5099,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>129</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>133771</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>113685</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>154491</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +5144,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>114483</t>
+          <t>113685</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>154160</t>
+          <t>154491</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,47 +5159,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>133771</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>114483</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>154160</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>31,54%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>27,0%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>36,35%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -7214,37 +5177,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72637</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57876</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>88668</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +5222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58353</t>
+          <t>57876</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>89695</t>
+          <t>88668</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,47 +5237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>72637</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>58353</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>89695</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>17,13%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>13,76%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>21,15%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -7327,37 +5255,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>401</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>424089</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>424089</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>424089</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7391,41 +5319,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>424089</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>424089</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>424089</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7444,37 +5337,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>484</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>530927</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>491596</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>574401</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +5382,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>495497</t>
+          <t>491596</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>576388</t>
+          <t>574401</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,47 +5397,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>530927</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>495497</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>576388</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>23,81%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>22,22%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>25,85%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -7557,37 +5415,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>882</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>924854</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>877262</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>976829</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +5460,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>876840</t>
+          <t>877262</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>971161</t>
+          <t>976829</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,47 +5475,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>882</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>924854</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>876840</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>971161</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>41,48%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>39,33%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>43,56%</t>
+          <t>43,81%</t>
         </is>
       </c>
     </row>
@@ -7670,37 +5493,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>476</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>492286</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>453646</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>531065</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +5538,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>453416</t>
+          <t>453646</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>532553</t>
+          <t>531065</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,47 +5553,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>476</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>492286</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>453416</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>532553</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>22,08%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>20,34%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>23,88%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -7783,37 +5571,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>269</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>281642</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>249725</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>312176</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +5616,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>249020</t>
+          <t>249725</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>315962</t>
+          <t>312176</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,47 +5631,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>281642</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>249020</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>315962</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>12,63%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>11,17%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>14,17%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -7896,37 +5649,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2229709</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2229709</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2229709</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7960,41 +5713,6 @@
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2111</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>2229709</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>2229709</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>2229709</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8008,13 +5726,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A9:A13"/>
     <mergeCell ref="A4:A8"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A19:A23"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="C1:I1"/>
   </mergeCells>
@@ -8028,7 +5745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8047,25 +5764,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última citología vaginal que le hicieron en 2023</t>
+          <t>Población según el tiempo transcurrido desde la última citología vaginal que le hicieron en 2023 (tasa de respuesta: 99,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -8076,7 +5786,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -8085,17 +5795,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -8166,41 +5865,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -8223,13 +5887,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -8244,37 +5901,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>324</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>164770</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>149338</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>176466</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +5946,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>149806</t>
+          <t>149338</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>177028</t>
+          <t>176466</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,47 +5961,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>164770</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>149806</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>177028</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>58,01%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>52,75%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>62,33%</t>
+          <t>62,13%</t>
         </is>
       </c>
     </row>
@@ -8357,37 +5979,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>73445</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>62902</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>90205</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +6024,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62854</t>
+          <t>62902</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90373</t>
+          <t>90205</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,47 +6039,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>73445</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>62854</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>90373</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>25,86%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>22,13%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>31,82%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -8470,37 +6057,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30195</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22465</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>38682</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +6102,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>22465</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>38682</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,47 +6117,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>30195</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>23006</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>38227</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>10,63%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>8,1%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -8583,37 +6135,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15609</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22899</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +6180,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>10045</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>22899</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,47 +6195,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>15609</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>10465</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>22581</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>5,5%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -8696,37 +6213,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>529</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>284019</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>284019</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>284019</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,41 +6277,6 @@
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>529</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>284019</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>284019</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>284019</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8813,37 +6295,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>371</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>315064</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>241106</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>467624</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +6340,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>244760</t>
+          <t>241106</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>493235</t>
+          <t>467624</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,47 +6355,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>315064</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>244760</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>493235</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>33,77%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>26,23%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>52,86%</t>
+          <t>50,12%</t>
         </is>
       </c>
     </row>
@@ -8926,37 +6373,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>484</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>300988</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>234425</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>341776</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +6418,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>220856</t>
+          <t>234425</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>339465</t>
+          <t>341776</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,47 +6433,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>300988</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>220856</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>339465</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>32,26%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>23,67%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>36,38%</t>
+          <t>36,63%</t>
         </is>
       </c>
     </row>
@@ -9039,37 +6451,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>291</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>191881</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>149337</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>222259</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +6496,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147148</t>
+          <t>149337</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>220827</t>
+          <t>222259</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,47 +6511,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>191881</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>147148</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>220827</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>20,56%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>15,77%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>23,67%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -9152,37 +6529,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>188</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>125147</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96739</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>149552</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +6574,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>92728</t>
+          <t>96739</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>145159</t>
+          <t>149552</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,47 +6589,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>125147</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>92728</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>145159</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>13,41%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>9,94%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>15,56%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -9265,37 +6607,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>933080</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>933080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>933080</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,41 +6671,6 @@
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1334</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>933080</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>933080</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>933080</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9382,37 +6689,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57422</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47919</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>69306</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +6734,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47227</t>
+          <t>47919</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69121</t>
+          <t>69306</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,47 +6749,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>57422</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>47227</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>69121</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>16,63%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>13,68%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>20,02%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -9495,37 +6767,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>197</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>123234</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>109159</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>139165</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +6812,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>108876</t>
+          <t>109159</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>140430</t>
+          <t>139165</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,47 +6827,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>123234</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>108876</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>140430</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>35,69%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>31,54%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>40,67%</t>
+          <t>40,31%</t>
         </is>
       </c>
     </row>
@@ -9608,37 +6845,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>145</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95723</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>82995</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>112538</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +6890,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>83076</t>
+          <t>82995</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>112324</t>
+          <t>112538</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,47 +6905,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>95723</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>83076</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>112324</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>27,73%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>24,06%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>32,53%</t>
+          <t>32,6%</t>
         </is>
       </c>
     </row>
@@ -9721,37 +6923,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>68874</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55156</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>83064</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +6968,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>54928</t>
+          <t>55156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>83686</t>
+          <t>83064</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,47 +6983,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>68874</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>54928</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>83686</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>19,95%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>15,91%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>24,24%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -9834,37 +7001,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>541</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>345252</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>345252</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>345252</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,41 +7065,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>541</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>345252</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>345252</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>345252</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9951,37 +7083,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>795</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>537256</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>468113</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>683077</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +7128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>471578</t>
+          <t>468113</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>720259</t>
+          <t>683077</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,47 +7143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>537256</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>471578</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>720259</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>34,39%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>30,18%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>46,1%</t>
+          <t>43,72%</t>
         </is>
       </c>
     </row>
@@ -10064,37 +7161,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>806</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>497666</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>426573</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>540193</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +7206,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>417266</t>
+          <t>426573</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>537878</t>
+          <t>540193</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,47 +7221,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>806</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>497666</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>417266</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>537878</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>31,85%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>26,71%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>34,43%</t>
+          <t>34,58%</t>
         </is>
       </c>
     </row>
@@ -10177,37 +7239,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>489</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>317798</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267362</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>351171</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +7284,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>264813</t>
+          <t>267362</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>350496</t>
+          <t>351171</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,47 +7299,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>317798</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>264813</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>350496</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>20,34%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>16,95%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>22,43%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -10290,37 +7317,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>314</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>209630</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>176378</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>236874</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +7362,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>176640</t>
+          <t>176378</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>237422</t>
+          <t>236874</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,47 +7377,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>209630</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>176640</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>237422</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>13,42%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>11,31%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>15,2%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -10403,37 +7395,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1562351</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1562351</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1562351</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10467,41 +7459,6 @@
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1562351</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1562351</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1562351</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10515,13 +7472,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A9:A13"/>
     <mergeCell ref="A4:A8"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A19:A23"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="C1:I1"/>
   </mergeCells>

--- a/data/trans_orig/P43D-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P43D-Estudios-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>189154</t>
+          <t>191808</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>234509</t>
+          <t>234112</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>189154</t>
+          <t>191808</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>234509</t>
+          <t>234112</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,25%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>123557</t>
+          <t>120806</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>163659</t>
+          <t>160931</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>123557</t>
+          <t>120806</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>163659</t>
+          <t>160931</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>91220</t>
+          <t>90819</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>129154</t>
+          <t>128400</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>91220</t>
+          <t>90819</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>129154</t>
+          <t>128400</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42039</t>
+          <t>41979</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67707</t>
+          <t>69866</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42039</t>
+          <t>41979</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67707</t>
+          <t>69866</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>144204</t>
+          <t>144372</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>193365</t>
+          <t>193838</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>144204</t>
+          <t>144372</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>193365</t>
+          <t>193838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>284222</t>
+          <t>284310</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>343851</t>
+          <t>340013</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>284222</t>
+          <t>284310</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>343851</t>
+          <t>340013</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>234307</t>
+          <t>236840</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>291327</t>
+          <t>292777</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>234307</t>
+          <t>236840</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>291327</t>
+          <t>292777</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,23%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>168434</t>
+          <t>168868</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>218707</t>
+          <t>216063</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>168434</t>
+          <t>168868</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>218707</t>
+          <t>216063</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29023</t>
+          <t>29538</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>53293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29023</t>
+          <t>29538</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51996</t>
+          <t>53293</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84602</t>
+          <t>83124</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>117539</t>
+          <t>117052</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>84602</t>
+          <t>83124</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>117539</t>
+          <t>117052</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,09%</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81915</t>
+          <t>81769</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>114786</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81915</t>
+          <t>81769</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114786</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,74%</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70616</t>
+          <t>70536</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101345</t>
+          <t>103097</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70616</t>
+          <t>70536</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101345</t>
+          <t>103097</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -1855,12 +1855,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>388118</t>
+          <t>383297</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>459721</t>
+          <t>456740</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>388118</t>
+          <t>383297</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>459721</t>
+          <t>456740</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>515341</t>
+          <t>512955</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>596654</t>
+          <t>594393</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>515341</t>
+          <t>512955</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>596654</t>
+          <t>594393</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -2011,12 +2011,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>430680</t>
+          <t>434950</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>505487</t>
+          <t>510469</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>430680</t>
+          <t>434950</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>505487</t>
+          <t>510469</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>298182</t>
+          <t>299895</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>364568</t>
+          <t>363947</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>298182</t>
+          <t>299895</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>364568</t>
+          <t>363947</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -2419,12 +2419,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>191704</t>
+          <t>191073</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>240056</t>
+          <t>241493</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>191704</t>
+          <t>191073</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>240056</t>
+          <t>241493</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -2497,12 +2497,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>205760</t>
+          <t>202930</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>257458</t>
+          <t>256701</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2512,12 +2512,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>205760</t>
+          <t>202930</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257458</t>
+          <t>256701</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -2575,12 +2575,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>131095</t>
+          <t>130903</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>173822</t>
+          <t>173044</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>131095</t>
+          <t>130903</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>173822</t>
+          <t>173044</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -2653,12 +2653,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86023</t>
+          <t>86679</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126226</t>
+          <t>125438</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2688,12 +2688,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86023</t>
+          <t>86679</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>126226</t>
+          <t>125438</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -2813,12 +2813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>170703</t>
+          <t>170669</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>223749</t>
+          <t>225633</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>170703</t>
+          <t>170669</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>223749</t>
+          <t>225633</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>419048</t>
+          <t>415559</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>488666</t>
+          <t>489259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>419048</t>
+          <t>415559</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>488666</t>
+          <t>489259</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,57%</t>
         </is>
       </c>
     </row>
@@ -2969,12 +2969,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>324652</t>
+          <t>323077</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>394753</t>
+          <t>393286</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>324652</t>
+          <t>323077</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>394753</t>
+          <t>393286</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -3047,12 +3047,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>205572</t>
+          <t>204033</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>265282</t>
+          <t>261485</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>205572</t>
+          <t>204033</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>265282</t>
+          <t>261485</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -3207,12 +3207,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23379</t>
+          <t>24647</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48868</t>
+          <t>49235</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23379</t>
+          <t>24647</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48868</t>
+          <t>49235</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3257,12 +3257,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>88966</t>
+          <t>90487</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>126520</t>
+          <t>126570</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>88966</t>
+          <t>90487</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>126520</t>
+          <t>126570</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3335,12 +3335,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,48%</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109674</t>
+          <t>109211</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>147130</t>
+          <t>147775</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>109674</t>
+          <t>109211</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>147130</t>
+          <t>147775</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -3441,12 +3441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61307</t>
+          <t>60272</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94205</t>
+          <t>92898</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3456,12 +3456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61307</t>
+          <t>60272</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>94205</t>
+          <t>92898</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>404683</t>
+          <t>407618</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>485935</t>
+          <t>489535</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>404683</t>
+          <t>407618</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>485935</t>
+          <t>489535</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -3679,12 +3679,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>743786</t>
+          <t>745956</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>840407</t>
+          <t>838151</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3694,12 +3694,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>743786</t>
+          <t>745956</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>840407</t>
+          <t>838151</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,65%</t>
         </is>
       </c>
     </row>
@@ -3757,12 +3757,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>591682</t>
+          <t>591057</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>684427</t>
+          <t>680923</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>591682</t>
+          <t>591057</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>684427</t>
+          <t>680923</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -3835,12 +3835,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>374451</t>
+          <t>376953</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>454898</t>
+          <t>454619</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>374451</t>
+          <t>376953</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>454898</t>
+          <t>454619</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,88%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>203260</t>
+          <t>204839</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>249716</t>
+          <t>250760</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>203260</t>
+          <t>204839</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>249716</t>
+          <t>250760</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,89%</t>
         </is>
       </c>
     </row>
@@ -4243,12 +4243,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>143531</t>
+          <t>144520</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>186376</t>
+          <t>188382</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>143531</t>
+          <t>144520</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186376</t>
+          <t>188382</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,48%</t>
         </is>
       </c>
     </row>
@@ -4321,12 +4321,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59404</t>
+          <t>58922</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92143</t>
+          <t>90400</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59404</t>
+          <t>58922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>92143</t>
+          <t>90400</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24948</t>
+          <t>24749</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47046</t>
+          <t>48490</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24948</t>
+          <t>24749</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47046</t>
+          <t>48490</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -4559,12 +4559,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>235367</t>
+          <t>233412</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>293629</t>
+          <t>291112</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>235367</t>
+          <t>233412</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>293629</t>
+          <t>291112</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -4637,12 +4637,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>545347</t>
+          <t>547028</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>618860</t>
+          <t>618170</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4652,12 +4652,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>545347</t>
+          <t>547028</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>618860</t>
+          <t>618170</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,44%</t>
         </is>
       </c>
     </row>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>256324</t>
+          <t>254559</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316384</t>
+          <t>312696</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>256324</t>
+          <t>254559</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>316384</t>
+          <t>312696</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -4793,12 +4793,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>149235</t>
+          <t>150472</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>201448</t>
+          <t>203319</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4828,12 +4828,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>149235</t>
+          <t>150472</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>201448</t>
+          <t>203319</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28605</t>
+          <t>28381</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53999</t>
+          <t>53951</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28605</t>
+          <t>28381</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53999</t>
+          <t>53951</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>157627</t>
+          <t>157665</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>198055</t>
+          <t>199918</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5046,12 +5046,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>157627</t>
+          <t>157665</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>198055</t>
+          <t>199918</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>47,14%</t>
         </is>
       </c>
     </row>
@@ -5109,12 +5109,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>113685</t>
+          <t>114168</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>154491</t>
+          <t>153182</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>113685</t>
+          <t>114168</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>154491</t>
+          <t>153182</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5159,12 +5159,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -5187,12 +5187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57876</t>
+          <t>56552</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>88668</t>
+          <t>89251</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57876</t>
+          <t>56552</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>88668</t>
+          <t>89251</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,05%</t>
         </is>
       </c>
     </row>
@@ -5347,12 +5347,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>491596</t>
+          <t>491657</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>574401</t>
+          <t>571775</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>491596</t>
+          <t>491657</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>574401</t>
+          <t>571775</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>877262</t>
+          <t>879533</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>976829</t>
+          <t>974978</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>877262</t>
+          <t>879533</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>976829</t>
+          <t>974978</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,73%</t>
         </is>
       </c>
     </row>
@@ -5503,12 +5503,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>453646</t>
+          <t>454375</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>531065</t>
+          <t>533130</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>453646</t>
+          <t>454375</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>531065</t>
+          <t>533130</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -5581,12 +5581,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>249725</t>
+          <t>251944</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>312176</t>
+          <t>315545</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>249725</t>
+          <t>251944</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>312176</t>
+          <t>315545</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -5906,32 +5906,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>164770</t>
+          <t>175399</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>149338</t>
+          <t>162914</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>176466</t>
+          <t>189360</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5941,32 +5941,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>164770</t>
+          <t>175399</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>149338</t>
+          <t>162914</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>176466</t>
+          <t>189360</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,75%</t>
         </is>
       </c>
     </row>
@@ -5984,32 +5984,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73445</t>
+          <t>75492</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62902</t>
+          <t>63390</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90205</t>
+          <t>88200</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6019,32 +6019,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>73445</t>
+          <t>75492</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62902</t>
+          <t>63390</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90205</t>
+          <t>88200</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -6062,32 +6062,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30195</t>
+          <t>34237</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22465</t>
+          <t>26732</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38682</t>
+          <t>44742</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6097,32 +6097,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30195</t>
+          <t>34237</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22465</t>
+          <t>26732</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38682</t>
+          <t>44742</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -6140,32 +6140,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>16628</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>11138</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22899</t>
+          <t>23096</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6175,32 +6175,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>16628</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>11138</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22899</t>
+          <t>23096</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -6218,17 +6218,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>284019</t>
+          <t>301756</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>284019</t>
+          <t>301756</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>284019</t>
+          <t>301756</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6253,17 +6253,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>284019</t>
+          <t>301756</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>284019</t>
+          <t>301756</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>284019</t>
+          <t>301756</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6300,32 +6300,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>315064</t>
+          <t>235550</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>241106</t>
+          <t>213859</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>467624</t>
+          <t>258223</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6335,32 +6335,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>315064</t>
+          <t>235550</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>241106</t>
+          <t>213859</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>467624</t>
+          <t>258223</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -6378,32 +6378,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>300988</t>
+          <t>332559</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>234425</t>
+          <t>307408</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>341776</t>
+          <t>358899</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6413,32 +6413,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>300988</t>
+          <t>332559</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>234425</t>
+          <t>307408</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>341776</t>
+          <t>358899</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -6456,32 +6456,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>191881</t>
+          <t>208295</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>149337</t>
+          <t>186503</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>222259</t>
+          <t>231876</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6491,32 +6491,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>191881</t>
+          <t>208295</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149337</t>
+          <t>186503</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>222259</t>
+          <t>231876</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -6534,32 +6534,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>125147</t>
+          <t>137139</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96739</t>
+          <t>120082</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>149552</t>
+          <t>156728</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6569,32 +6569,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>125147</t>
+          <t>137139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>96739</t>
+          <t>120082</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>149552</t>
+          <t>156728</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -6612,17 +6612,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>933080</t>
+          <t>913542</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>933080</t>
+          <t>913542</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>933080</t>
+          <t>913542</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6647,17 +6647,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>933080</t>
+          <t>913542</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>933080</t>
+          <t>913542</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>933080</t>
+          <t>913542</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6694,32 +6694,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>57422</t>
+          <t>65748</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47919</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69306</t>
+          <t>78742</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6729,32 +6729,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>57422</t>
+          <t>65748</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47919</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69306</t>
+          <t>78742</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -6772,32 +6772,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>123234</t>
+          <t>136659</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>109159</t>
+          <t>121632</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>139165</t>
+          <t>154851</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6807,32 +6807,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>123234</t>
+          <t>136659</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>109159</t>
+          <t>121632</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>139165</t>
+          <t>154851</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,19%</t>
         </is>
       </c>
     </row>
@@ -6850,32 +6850,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>95723</t>
+          <t>106908</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82995</t>
+          <t>91772</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112538</t>
+          <t>122332</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6885,32 +6885,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>95723</t>
+          <t>106908</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>82995</t>
+          <t>91772</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>112538</t>
+          <t>122332</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -6928,32 +6928,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>68874</t>
+          <t>76012</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55156</t>
+          <t>62639</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83064</t>
+          <t>90587</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>68874</t>
+          <t>76012</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>55156</t>
+          <t>62639</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>83064</t>
+          <t>90587</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -7006,17 +7006,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>345252</t>
+          <t>385326</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>345252</t>
+          <t>385326</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>345252</t>
+          <t>385326</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7041,17 +7041,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>345252</t>
+          <t>385326</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>345252</t>
+          <t>385326</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>345252</t>
+          <t>385326</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7088,32 +7088,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>537256</t>
+          <t>476696</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>468113</t>
+          <t>448840</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>683077</t>
+          <t>506770</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7123,32 +7123,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>537256</t>
+          <t>476696</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>468113</t>
+          <t>448840</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>683077</t>
+          <t>506770</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -7166,32 +7166,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>497666</t>
+          <t>544710</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>426573</t>
+          <t>513624</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>540193</t>
+          <t>577350</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7201,32 +7201,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>497666</t>
+          <t>544710</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>426573</t>
+          <t>513624</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>540193</t>
+          <t>577350</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>36,07%</t>
         </is>
       </c>
     </row>
@@ -7244,32 +7244,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>317798</t>
+          <t>349440</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>267362</t>
+          <t>322756</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>351171</t>
+          <t>379489</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7279,32 +7279,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>317798</t>
+          <t>349440</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>267362</t>
+          <t>322756</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>351171</t>
+          <t>379489</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -7322,32 +7322,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>209630</t>
+          <t>229778</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>176378</t>
+          <t>205131</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>236874</t>
+          <t>255106</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7357,32 +7357,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>209630</t>
+          <t>229778</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>176378</t>
+          <t>205131</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>236874</t>
+          <t>255106</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -7400,17 +7400,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1562351</t>
+          <t>1600624</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1562351</t>
+          <t>1600624</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1562351</t>
+          <t>1600624</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7435,17 +7435,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1562351</t>
+          <t>1600624</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1562351</t>
+          <t>1600624</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1562351</t>
+          <t>1600624</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
